--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96d58a0df60135d6/Dashboard 0.2/Tasks/CoverLettermaker/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96d58a0df60135d6/Dashboard 0.2/Tasks/CoverLettermaker/AB-Coder96/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1336" documentId="11_F25DC773A252ABDACC10489F515D40A65BDE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CADB1C71-2358-495C-B2BB-B33725B568F2}"/>
+  <xr:revisionPtr revIDLastSave="1347" documentId="11_F25DC773A252ABDACC10489F515D40A65BDE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79A3F16B-150C-465C-A204-42F3A811C4D6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="340" windowWidth="21640" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="263">
   <si>
     <t>Affilation 1</t>
   </si>
@@ -821,6 +821,12 @@
   </si>
   <si>
     <t>Mathpower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigSILENT </t>
+  </si>
+  <si>
+    <t>Helioscope</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1079,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1102,14 +1108,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1158,36 +1160,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1202,11 +1176,39 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1224,6 +1226,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1495,7 +1501,7 @@
     <col min="1" max="1" width="24.7265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.81640625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.81640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.81640625" style="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38.26953125" style="1" customWidth="1"/>
     <col min="6" max="6" width="5.81640625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.54296875" style="1"/>
@@ -1508,60 +1514,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="35" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="34" t="s">
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
     </row>
     <row r="2" spans="1:12" ht="42" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="I2" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="J2" s="36" t="s">
         <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="14" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1569,31 +1575,31 @@
       <c r="A3" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="43">
-        <v>5</v>
-      </c>
-      <c r="C3" s="52" t="s">
+      <c r="B3" s="46">
+        <v>5</v>
+      </c>
+      <c r="C3" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="18">
         <v>5</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="43">
+      <c r="F3" s="32">
         <v>5</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="H3" s="45">
+      <c r="H3" s="33">
         <v>5</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="J3" s="49">
+      <c r="J3" s="37">
         <v>5</v>
       </c>
       <c r="K3" s="6" t="s">
@@ -1607,34 +1613,34 @@
       <c r="A4" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="42">
-        <v>5</v>
-      </c>
-      <c r="C4" s="53" t="s">
+      <c r="B4" s="12">
+        <v>5</v>
+      </c>
+      <c r="C4" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="21">
-        <v>5</v>
-      </c>
-      <c r="E4" s="41" t="s">
+      <c r="D4" s="19">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="4">
         <v>5</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="44">
+      <c r="H4" s="3">
         <v>4.5</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="J4" s="50">
-        <v>5</v>
-      </c>
-      <c r="K4" s="41" t="s">
+      <c r="J4" s="38">
+        <v>5</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L4" s="9">
@@ -1645,34 +1651,34 @@
       <c r="A5" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="42">
-        <v>5</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="12">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="22">
-        <v>5</v>
-      </c>
-      <c r="E5" s="41" t="s">
+      <c r="D5" s="20">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="4">
         <v>5</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="44">
+      <c r="H5" s="3">
         <v>4</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="J5" s="50">
-        <v>5</v>
-      </c>
-      <c r="K5" s="41" t="s">
+      <c r="J5" s="38">
+        <v>5</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>58</v>
       </c>
       <c r="L5" s="9">
@@ -1683,34 +1689,34 @@
       <c r="A6" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="42">
-        <v>5</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="12">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="22">
-        <v>5</v>
-      </c>
-      <c r="E6" s="41" t="s">
+      <c r="D6" s="20">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="4">
         <v>5</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="44">
+      <c r="H6" s="3">
         <v>5</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="J6" s="50">
-        <v>5</v>
-      </c>
-      <c r="K6" s="41" t="s">
+      <c r="J6" s="38">
+        <v>5</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>62</v>
       </c>
       <c r="L6" s="9">
@@ -1721,34 +1727,34 @@
       <c r="A7" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="42">
-        <v>5</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="12">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="20">
         <v>4</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="4">
         <v>5</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H7" s="3">
         <v>4</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J7" s="50">
-        <v>5</v>
-      </c>
-      <c r="K7" s="41" t="s">
+      <c r="J7" s="38">
+        <v>5</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>67</v>
       </c>
       <c r="L7" s="9">
@@ -1759,34 +1765,34 @@
       <c r="A8" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="42">
-        <v>5</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="12">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="20">
         <v>4</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="4">
         <v>5</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="44">
+      <c r="H8" s="3">
         <v>3.5</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="J8" s="50">
+      <c r="J8" s="38">
         <v>4</v>
       </c>
-      <c r="K8" s="41" t="s">
+      <c r="K8" s="1" t="s">
         <v>68</v>
       </c>
       <c r="L8" s="9">
@@ -1797,16 +1803,16 @@
       <c r="A9" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="42">
-        <v>5</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="12">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="22">
-        <v>5</v>
-      </c>
-      <c r="E9" s="41" t="s">
+      <c r="D9" s="20">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F9" s="4">
@@ -1815,16 +1821,16 @@
       <c r="G9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="44">
+      <c r="H9" s="3">
         <v>4</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="J9" s="50">
+      <c r="J9" s="38">
         <v>4</v>
       </c>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="1" t="s">
         <v>63</v>
       </c>
       <c r="L9" s="9">
@@ -1835,16 +1841,16 @@
       <c r="A10" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B10" s="42">
-        <v>5</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="12">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <v>4</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F10" s="4">
@@ -1853,16 +1859,16 @@
       <c r="G10" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="H10" s="44">
+      <c r="H10" s="3">
         <v>4</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="J10" s="50">
-        <v>5</v>
-      </c>
-      <c r="K10" s="41" t="s">
+      <c r="J10" s="38">
+        <v>5</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L10" s="9">
@@ -1873,34 +1879,34 @@
       <c r="A11" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="42">
-        <v>5</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="12">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="22">
-        <v>5</v>
-      </c>
-      <c r="E11" s="41" t="s">
+      <c r="D11" s="20">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="4">
         <v>5</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="H11" s="46">
+      <c r="H11" s="34">
         <v>3</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="J11" s="50">
-        <v>5</v>
-      </c>
-      <c r="K11" s="41" t="s">
+      <c r="J11" s="38">
+        <v>5</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>65</v>
       </c>
       <c r="L11" s="9">
@@ -1911,28 +1917,34 @@
       <c r="A12" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="42">
-        <v>5</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="12">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="20">
         <v>3</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="1" t="s">
         <v>83</v>
       </c>
       <c r="F12" s="12">
         <v>5</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="J12" s="50">
-        <v>5</v>
-      </c>
-      <c r="K12" s="41" t="s">
+      <c r="J12" s="38">
+        <v>5</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>66</v>
       </c>
       <c r="L12" s="9">
@@ -1943,16 +1955,16 @@
       <c r="A13" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="42">
-        <v>5</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="12">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <v>2.5</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F13" s="12">
@@ -1961,10 +1973,10 @@
       <c r="I13" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="J13" s="50">
+      <c r="J13" s="38">
         <v>4</v>
       </c>
-      <c r="K13" s="41" t="s">
+      <c r="K13" s="1" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="9">
@@ -1975,16 +1987,16 @@
       <c r="A14" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="42">
-        <v>5</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="12">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="20">
         <v>4</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F14" s="12">
@@ -1993,10 +2005,10 @@
       <c r="I14" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="J14" s="50">
-        <v>5</v>
-      </c>
-      <c r="K14" s="41" t="s">
+      <c r="J14" s="38">
+        <v>5</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>57</v>
       </c>
       <c r="L14" s="9">
@@ -2007,16 +2019,16 @@
       <c r="A15" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="42">
-        <v>5</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B15" s="12">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D15" s="23">
-        <v>5</v>
-      </c>
-      <c r="E15" s="41" t="s">
+      <c r="D15" s="20">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>85</v>
       </c>
       <c r="F15" s="12">
@@ -2025,10 +2037,10 @@
       <c r="I15" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="J15" s="50">
-        <v>5</v>
-      </c>
-      <c r="K15" s="41" t="s">
+      <c r="J15" s="38">
+        <v>5</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>69</v>
       </c>
       <c r="L15" s="9">
@@ -2042,7 +2054,13 @@
       <c r="B16" s="12">
         <v>5</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="C16" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="D16" s="21">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>90</v>
       </c>
       <c r="F16" s="12">
@@ -2051,10 +2069,10 @@
       <c r="I16" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="J16" s="50">
-        <v>5</v>
-      </c>
-      <c r="K16" s="41" t="s">
+      <c r="J16" s="38">
+        <v>5</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>61</v>
       </c>
       <c r="L16" s="9">
@@ -2077,10 +2095,10 @@
       <c r="I17" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="J17" s="50">
-        <v>5</v>
-      </c>
-      <c r="K17" s="41" t="s">
+      <c r="J17" s="38">
+        <v>5</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>59</v>
       </c>
       <c r="L17" s="9">
@@ -2103,8 +2121,8 @@
       <c r="I18" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="J18" s="51"/>
-      <c r="K18" s="41" t="s">
+      <c r="J18" s="39"/>
+      <c r="K18" s="1" t="s">
         <v>60</v>
       </c>
       <c r="L18" s="9">
@@ -2216,7 +2234,7 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="8" t="s">
         <v>123</v>
       </c>
       <c r="B26" s="12">
@@ -2230,7 +2248,7 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="8" t="s">
         <v>256</v>
       </c>
       <c r="B27" s="12">
@@ -2244,10 +2262,10 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="12">
         <v>5</v>
       </c>
       <c r="E28" s="8" t="s">
@@ -2258,6 +2276,12 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="13">
+        <v>3</v>
+      </c>
       <c r="E29" s="8" t="s">
         <v>91</v>
       </c>
@@ -2332,714 +2356,714 @@
   <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="56.1796875" style="28" customWidth="1"/>
-    <col min="2" max="2" width="80.81640625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="33.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.26953125" style="26" customWidth="1"/>
+    <col min="1" max="1" width="56.1796875" style="26" customWidth="1"/>
+    <col min="2" max="2" width="80.81640625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="33.453125" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7265625" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="22" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="E2" s="25"/>
+      <c r="E2" s="23"/>
     </row>
     <row r="3" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="25"/>
+      <c r="E3" s="23"/>
     </row>
     <row r="4" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:5" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="39"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="32" t="s">
+      <c r="A6" s="52"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="E6" s="25"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="29"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="39"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="32" t="s">
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="E8" s="25"/>
+      <c r="E8" s="23"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="E9" s="25"/>
+      <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="39"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="32" t="s">
+      <c r="A10" s="52"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="25"/>
+      <c r="E10" s="23"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="E11" s="25"/>
+      <c r="E11" s="23"/>
     </row>
     <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="39"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="32" t="s">
+      <c r="A12" s="52"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E12" s="23"/>
     </row>
     <row r="13" spans="1:5" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="23"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="51" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="E14" s="25"/>
+      <c r="E14" s="23"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="39"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="32" t="s">
+      <c r="A15" s="52"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="E15" s="25"/>
+      <c r="E15" s="23"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="E16" s="25"/>
+      <c r="E16" s="23"/>
     </row>
     <row r="17" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="39"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="32" t="s">
+      <c r="A17" s="52"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="E17" s="25"/>
+      <c r="E17" s="23"/>
     </row>
     <row r="18" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="25"/>
+      <c r="E18" s="23"/>
     </row>
     <row r="19" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E19" s="25"/>
+      <c r="E19" s="23"/>
     </row>
     <row r="20" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="E20" s="30"/>
+      <c r="E20" s="28"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="E21" s="25"/>
+      <c r="E21" s="23"/>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="39"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="32" t="s">
+      <c r="A22" s="52"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="E22" s="25"/>
+      <c r="E22" s="23"/>
     </row>
     <row r="23" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="25"/>
+      <c r="E23" s="23"/>
     </row>
     <row r="24" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="25"/>
+      <c r="E24" s="23"/>
     </row>
     <row r="25" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="25"/>
+      <c r="E25" s="23"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="D26" s="33" t="s">
+      <c r="D26" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="25"/>
+      <c r="E26" s="23"/>
     </row>
     <row r="27" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="39"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="32" t="s">
+      <c r="A27" s="52"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="E27" s="25"/>
+      <c r="E27" s="23"/>
     </row>
     <row r="28" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="25"/>
+      <c r="E28" s="23"/>
     </row>
     <row r="29" spans="1:5" ht="33.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="C29" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="32" t="s">
+      <c r="C29" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="25"/>
+      <c r="E29" s="23"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="38" t="s">
+      <c r="B30" s="51" t="s">
         <v>218</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="25"/>
+      <c r="E30" s="23"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="40"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="33" t="s">
+      <c r="A31" s="53"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="E31" s="25"/>
+      <c r="E31" s="23"/>
     </row>
     <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="39"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="32" t="s">
+      <c r="A32" s="52"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="E32" s="25"/>
+      <c r="E32" s="23"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="38" t="s">
+      <c r="B33" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="C33" s="51" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="E33" s="25"/>
+      <c r="E33" s="23"/>
     </row>
     <row r="34" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="39"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="32" t="s">
+      <c r="A34" s="52"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="E34" s="25"/>
+      <c r="E34" s="23"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="38" t="s">
+      <c r="A35" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="51" t="s">
         <v>224</v>
       </c>
-      <c r="C35" s="38" t="s">
+      <c r="C35" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="D35" s="33" t="s">
+      <c r="D35" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="E35" s="25"/>
+      <c r="E35" s="23"/>
     </row>
     <row r="36" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="39"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="32" t="s">
+      <c r="A36" s="52"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="E36" s="25"/>
+      <c r="E36" s="23"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="38" t="s">
+      <c r="A37" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="51" t="s">
         <v>226</v>
       </c>
-      <c r="C37" s="38" t="s">
+      <c r="C37" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="33" t="s">
+      <c r="D37" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="E37" s="25"/>
+      <c r="E37" s="23"/>
     </row>
     <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="39"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="32" t="s">
+      <c r="A38" s="52"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="E38" s="25"/>
+      <c r="E38" s="23"/>
     </row>
     <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="25"/>
+      <c r="E39" s="23"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="38" t="s">
+      <c r="A40" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="B40" s="38" t="s">
+      <c r="B40" s="51" t="s">
         <v>228</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="E40" s="25"/>
+      <c r="E40" s="23"/>
     </row>
     <row r="41" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="39"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="32" t="s">
+      <c r="A41" s="52"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="E41" s="25"/>
+      <c r="E41" s="23"/>
     </row>
     <row r="42" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="C42" s="32" t="s">
+      <c r="C42" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="D42" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="E42" s="25"/>
+      <c r="E42" s="23"/>
     </row>
     <row r="43" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="B43" s="32" t="s">
+      <c r="B43" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="32" t="s">
+      <c r="C43" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="E43" s="25"/>
+      <c r="E43" s="23"/>
     </row>
     <row r="44" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="B44" s="32" t="s">
+      <c r="B44" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="32" t="s">
+      <c r="C44" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E44" s="25"/>
+      <c r="E44" s="23"/>
     </row>
     <row r="45" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="B45" s="32" t="s">
+      <c r="B45" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="C45" s="32" t="s">
+      <c r="C45" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="D45" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E45" s="25"/>
+      <c r="E45" s="23"/>
     </row>
     <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="31" t="s">
+      <c r="A46" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="B46" s="32" t="s">
+      <c r="B46" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="C46" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="25"/>
+      <c r="E46" s="23"/>
     </row>
     <row r="47" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="C47" s="32" t="s">
+      <c r="C47" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E47" s="25"/>
+      <c r="E47" s="23"/>
     </row>
     <row r="48" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B48" s="32" t="s">
+      <c r="B48" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="C48" s="32" t="s">
+      <c r="C48" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="32" t="s">
+      <c r="D48" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E48" s="25"/>
+      <c r="E48" s="23"/>
     </row>
     <row r="49" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="B49" s="32" t="s">
+      <c r="B49" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="32" t="s">
+      <c r="C49" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D49" s="32" t="s">
+      <c r="D49" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="25"/>
+      <c r="E49" s="23"/>
     </row>
     <row r="50" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="B50" s="32" t="s">
+      <c r="B50" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="C50" s="32" t="s">
+      <c r="C50" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="32" t="s">
+      <c r="D50" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="25"/>
+      <c r="E50" s="23"/>
     </row>
     <row r="51" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B51" s="32" t="s">
+      <c r="B51" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="C51" s="32" t="s">
+      <c r="C51" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="D51" s="32" t="s">
+      <c r="D51" s="30" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="38" t="s">
+      <c r="A52" s="51" t="s">
         <v>248</v>
       </c>
-      <c r="B52" s="38" t="s">
+      <c r="B52" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="C52" s="38" t="s">
+      <c r="C52" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D52" s="33" t="s">
+      <c r="D52" s="31" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="39"/>
-      <c r="B53" s="39"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="32" t="s">
+      <c r="A53" s="52"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="30" t="s">
         <v>250</v>
       </c>
     </row>
